--- a/lead_generation_forms/035_lead_qualification_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/035_lead_qualification_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -891,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'qualified'}</t>
+          <t>qualified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Qualified'}</t>
+          <t>Qualified</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_qualified'}</t>
+          <t>not_qualified</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Not Qualified'}</t>
+          <t>Not Qualified</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'qualified_but_not_yet_ready'}</t>
+          <t>qualified_but_not_yet_ready</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Qualified but not yet ready'}</t>
+          <t>Qualified but not yet ready</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'sales_team'}</t>
+          <t>sales_team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Sales Team'}</t>
+          <t>Sales Team</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'not_ready'}</t>
+          <t>not_ready</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Not Ready'}</t>
+          <t>Not Ready</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_qualified'}</t>
+          <t>not_qualified</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Qualified'}</t>
+          <t>Not Qualified</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1043,29 +1043,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'qualified_but_not_yet_ready'}</t>
+          <t>qualified_but_not_yet_ready</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Qualified but not yet ready'}</t>
+          <t>Qualified but not yet ready</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lead_reason_for_ineligibility_choices</t>
+          <t>assigned_sales_person_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1077,29 +1077,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_sales_person_choices</t>
+          <t>next_step_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1111,27 +1111,10 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>next_step_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
